--- a/Backtest/05-01-18/S&P500stock_05-01-18period252RS90.xlsx
+++ b/Backtest/05-01-18/S&P500stock_05-01-18period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
   <si>
     <t>Stock</t>
   </si>
@@ -127,193 +127,148 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>MU</t>
-  </si>
-  <si>
-    <t>FMC</t>
-  </si>
-  <si>
-    <t>TTWO</t>
-  </si>
-  <si>
-    <t>MCO</t>
+    <t>AMZN</t>
   </si>
   <si>
     <t>NFLX</t>
   </si>
   <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>ELV</t>
-  </si>
-  <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>BA</t>
+    <t>CSGP</t>
+  </si>
+  <si>
+    <t>PGR</t>
   </si>
   <si>
     <t>ADBE</t>
   </si>
   <si>
-    <t>MSCI</t>
-  </si>
-  <si>
-    <t>NVR</t>
-  </si>
-  <si>
-    <t>TER</t>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>CZR</t>
   </si>
   <si>
     <t>MTCH</t>
   </si>
   <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>NRG</t>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>LW</t>
   </si>
   <si>
     <t>PODD</t>
   </si>
   <si>
-    <t>AVY</t>
-  </si>
-  <si>
-    <t>MV</t>
-  </si>
-  <si>
-    <t>M</t>
+    <t>PAYC</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>2018-01-25</t>
-  </si>
-  <si>
-    <t>2018-03-22</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-07</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-01-22</t>
-  </si>
-  <si>
-    <t>2018-02-14</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-08</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2018-01-24</t>
-  </si>
-  <si>
-    <t>2018-02-15</t>
-  </si>
-  <si>
-    <t>2018-03-01</t>
-  </si>
-  <si>
-    <t>2018-02-21</t>
-  </si>
-  <si>
-    <t>Industrials</t>
+    <t>2018-07-26</t>
+  </si>
+  <si>
+    <t>2018-07-16</t>
+  </si>
+  <si>
+    <t>2018-07-24</t>
+  </si>
+  <si>
+    <t>2018-07-17</t>
+  </si>
+  <si>
+    <t>2018-06-14</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-05-03</t>
+  </si>
+  <si>
+    <t>2018-05-09</t>
+  </si>
+  <si>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>2018-07-31</t>
+  </si>
+  <si>
+    <t>2018-06-04</t>
+  </si>
+  <si>
+    <t>2018-07-25</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
-    <t>Utilities</t>
-  </si>
-  <si>
-    <t>Farm &amp; Heavy Construction Machinery</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Agricultural Inputs</t>
-  </si>
-  <si>
-    <t>Electronic Gaming &amp; Multimedia</t>
-  </si>
-  <si>
-    <t>Financial Data &amp; Stock Exchanges</t>
+    <t>Internet Retail</t>
   </si>
   <si>
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Lodging</t>
-  </si>
-  <si>
-    <t>Healthcare Plans</t>
-  </si>
-  <si>
-    <t>Computer Hardware</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
+    <t>Real Estate Services</t>
+  </si>
+  <si>
+    <t>Insurance - Property &amp; Casualty</t>
   </si>
   <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
+    <t>Resorts &amp; Casinos</t>
   </si>
   <si>
     <t>Internet Content &amp; Information</t>
   </si>
   <si>
-    <t>Utilities - Independent Power Producers</t>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
   </si>
   <si>
     <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Packaging &amp; Containers</t>
   </si>
 </sst>
 </file>
@@ -671,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -792,52 +747,49 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>94.40993788819875</v>
+        <v>96.07438016528926</v>
       </c>
       <c r="C2">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>159.44</v>
+        <v>78.31</v>
       </c>
       <c r="E2">
-        <v>1.09</v>
+        <v>2.23</v>
       </c>
       <c r="F2">
-        <v>-0.4187539767300951</v>
+        <v>0.3930368773426112</v>
       </c>
       <c r="G2">
-        <v>1.15</v>
+        <v>2.27</v>
       </c>
       <c r="H2">
-        <v>-0.8928266501979568</v>
+        <v>0.2145301906851969</v>
       </c>
       <c r="I2">
-        <v>157.9519989013672</v>
+        <v>75.76970062255859</v>
       </c>
       <c r="J2">
-        <v>151.1565010070801</v>
+        <v>73.65159950256347</v>
       </c>
       <c r="K2">
-        <v>142.9878005981445</v>
+        <v>75.11203002929688</v>
       </c>
       <c r="L2">
-        <v>118.0361999893188</v>
+        <v>60.35724739074707</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>1.1</v>
-      </c>
-      <c r="O2" t="s">
-        <v>57</v>
+        <v>1.01</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -846,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>3.333333333333333</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -858,46 +810,46 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>90.34</v>
+        <v>46.35</v>
       </c>
       <c r="Y2">
-        <v>159.58</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z2">
-        <v>74.84</v>
+        <v>720.78</v>
       </c>
       <c r="AA2">
-        <v>0.24</v>
+        <v>-67438.02</v>
       </c>
       <c r="AB2">
-        <v>777.27</v>
+        <v>39.49</v>
       </c>
       <c r="AC2">
-        <v>189.95</v>
+        <v>719.51</v>
       </c>
       <c r="AD2">
-        <v>6.76</v>
+        <v>5.18</v>
       </c>
       <c r="AE2">
-        <v>31.62</v>
+        <v>-12.95</v>
       </c>
       <c r="AF2">
-        <v>312.12</v>
+        <v>628.3</v>
       </c>
       <c r="AG2">
-        <v>116.58</v>
+        <v>29.27</v>
       </c>
       <c r="AH2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AI2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AK2">
-        <v>87.6595456799311</v>
+        <v>36.3495658759885</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -905,44 +857,44 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>98.75776397515527</v>
+        <v>98.96694214876032</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>46.88</v>
+        <v>312.46</v>
       </c>
       <c r="E3">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="F3">
-        <v>2.878037722709775</v>
+        <v>0.9476287901573391</v>
       </c>
       <c r="G3">
-        <v>2.64</v>
+        <v>2.99</v>
       </c>
       <c r="H3">
-        <v>1.455472924020853</v>
+        <v>1.408821973881139</v>
       </c>
       <c r="I3">
-        <v>43.69199981689453</v>
+        <v>310.1960021972656</v>
       </c>
       <c r="J3">
-        <v>43.23599987030029</v>
+        <v>308.8250015258789</v>
       </c>
       <c r="K3">
-        <v>43.93919998168946</v>
+        <v>305.8382012939453</v>
       </c>
       <c r="L3">
-        <v>34.54915004730225</v>
+        <v>224.8301002502441</v>
       </c>
       <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
         <v>1.01</v>
       </c>
-      <c r="N3">
-        <v>0.99</v>
-      </c>
       <c r="P3">
         <v>0</v>
       </c>
@@ -962,52 +914,52 @@
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
       </c>
       <c r="X3">
-        <v>21.49</v>
+        <v>144.25</v>
       </c>
       <c r="Y3">
-        <v>49.89</v>
+        <v>338.82</v>
       </c>
       <c r="Z3">
-        <v>51.93</v>
+        <v>133.01</v>
       </c>
       <c r="AA3">
-        <v>-70</v>
+        <v>1683.46</v>
       </c>
       <c r="AB3">
-        <v>1245.1</v>
+        <v>64.89</v>
       </c>
       <c r="AC3">
-        <v>191.36</v>
+        <v>346.67</v>
       </c>
       <c r="AD3">
-        <v>11.45</v>
+        <v>7.22</v>
       </c>
       <c r="AE3">
-        <v>7.27</v>
+        <v>55.81</v>
       </c>
       <c r="AF3">
-        <v>47.65</v>
+        <v>43.33</v>
       </c>
       <c r="AG3">
-        <v>83.95</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="AI3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="AJ3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AK3">
-        <v>87.51431975832963</v>
+        <v>34.03126863140002</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1015,52 +967,49 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>93.58178053830227</v>
+        <v>92.35537190082644</v>
       </c>
       <c r="C4">
-        <v>349</v>
+        <v>207</v>
       </c>
       <c r="D4">
-        <v>84.52</v>
+        <v>36.67</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>1.79</v>
       </c>
       <c r="F4">
-        <v>-0.6030466804254917</v>
+        <v>-0.1374423436106069</v>
       </c>
       <c r="G4">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="H4">
-        <v>-0.877066250370985</v>
+        <v>-0.8636498913666947</v>
       </c>
       <c r="I4">
-        <v>83.22636413574219</v>
+        <v>37.23139953613281</v>
       </c>
       <c r="J4">
-        <v>80.73243675231933</v>
+        <v>36.66984977722168</v>
       </c>
       <c r="K4">
-        <v>80.63295761108398</v>
+        <v>36.1293399810791</v>
       </c>
       <c r="L4">
-        <v>71.64492610931397</v>
+        <v>31.24542496681213</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
         <v>1.03</v>
       </c>
-      <c r="O4" t="s">
-        <v>57</v>
-      </c>
       <c r="P4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1069,58 +1018,55 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>49.03</v>
+        <v>23.89</v>
       </c>
       <c r="Y4">
-        <v>85.59</v>
+        <v>39.21</v>
       </c>
       <c r="Z4">
-        <v>10.53</v>
+        <v>13.18</v>
       </c>
       <c r="AA4">
-        <v>0.25</v>
+        <v>6191.14</v>
       </c>
       <c r="AB4">
-        <v>220</v>
+        <v>28.08</v>
       </c>
       <c r="AC4">
-        <v>241.67</v>
-      </c>
-      <c r="AD4">
-        <v>3.32</v>
+        <v>114.71</v>
       </c>
       <c r="AE4">
-        <v>-26.79</v>
+        <v>14.06</v>
       </c>
       <c r="AF4">
-        <v>160.22</v>
+        <v>21.9</v>
       </c>
       <c r="AG4">
-        <v>-875</v>
+        <v>54.41</v>
       </c>
       <c r="AH4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="AI4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="AJ4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK4">
-        <v>80.01726081487919</v>
+        <v>18.88263913887333</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1128,40 +1074,40 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>99.58592132505176</v>
+        <v>92.14876033057851</v>
       </c>
       <c r="C5">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="D5">
-        <v>114.02</v>
+        <v>60.29</v>
       </c>
       <c r="E5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="F5">
-        <v>-0.3368461084210304</v>
+        <v>-0.9693302128326988</v>
       </c>
       <c r="G5">
-        <v>2.11</v>
+        <v>1.54</v>
       </c>
       <c r="H5">
-        <v>0.6201717331913433</v>
+        <v>-0.9963489783884661</v>
       </c>
       <c r="I5">
-        <v>112.029997253418</v>
+        <v>60.58199996948242</v>
       </c>
       <c r="J5">
-        <v>109.3094993591309</v>
+        <v>60.75200004577637</v>
       </c>
       <c r="K5">
-        <v>111.1458000183106</v>
+        <v>59.99699989318847</v>
       </c>
       <c r="L5">
-        <v>88.20689992904663</v>
+        <v>53.02809995651245</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>1.01</v>
@@ -1182,55 +1128,55 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>49.32</v>
+        <v>38.75</v>
       </c>
       <c r="Y5">
-        <v>120.62</v>
+        <v>62.78</v>
       </c>
       <c r="Z5">
-        <v>11.19</v>
+        <v>35.68</v>
       </c>
       <c r="AA5">
-        <v>-15.04</v>
+        <v>14.28</v>
       </c>
       <c r="AB5">
-        <v>485.29</v>
+        <v>20.45</v>
       </c>
       <c r="AC5">
-        <v>90.91</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="AD5">
-        <v>-0.19</v>
+        <v>7.42</v>
       </c>
       <c r="AE5">
-        <v>-105.26</v>
+        <v>24.24</v>
       </c>
       <c r="AF5">
-        <v>-48.18</v>
+        <v>153.85</v>
       </c>
       <c r="AG5">
-        <v>433.33</v>
+        <v>-38.1</v>
       </c>
       <c r="AH5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="AJ5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AK5">
-        <v>70.83380510197651</v>
+        <v>14.57000247054467</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1238,49 +1184,49 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>90.47619047619048</v>
+        <v>95.04132231404959</v>
       </c>
       <c r="C6">
-        <v>414</v>
+        <v>241</v>
       </c>
       <c r="D6">
-        <v>151.6</v>
+        <v>221.6</v>
       </c>
       <c r="E6">
-        <v>0.88</v>
+        <v>1.77</v>
       </c>
       <c r="F6">
-        <v>-0.8487702853526869</v>
+        <v>-0.1615550354721168</v>
       </c>
       <c r="G6">
-        <v>0.89</v>
+        <v>2.15</v>
       </c>
       <c r="H6">
-        <v>-1.302597045699226</v>
+        <v>0.01548156015253975</v>
       </c>
       <c r="I6">
-        <v>148.40400390625</v>
+        <v>220.1240020751953</v>
       </c>
       <c r="J6">
-        <v>149.4835014343262</v>
+        <v>223.4520011901855</v>
       </c>
       <c r="K6">
-        <v>147.7258001708984</v>
+        <v>218.2594003295899</v>
       </c>
       <c r="L6">
-        <v>131.1256503677368</v>
+        <v>180.9252501678467</v>
       </c>
       <c r="M6">
         <v>0.99</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1289,58 +1235,58 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>6.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>93.51000000000001</v>
+        <v>130.82</v>
       </c>
       <c r="Y6">
-        <v>153.86</v>
+        <v>233.17</v>
       </c>
       <c r="Z6">
-        <v>27.02</v>
+        <v>104.45</v>
       </c>
       <c r="AA6">
-        <v>4.65</v>
+        <v>30.06</v>
       </c>
       <c r="AB6">
-        <v>16.13</v>
+        <v>11.44</v>
       </c>
       <c r="AC6">
-        <v>174.77</v>
+        <v>55.26</v>
       </c>
       <c r="AD6">
-        <v>-203.89</v>
+        <v>6.75</v>
       </c>
       <c r="AE6">
-        <v>1.84</v>
+        <v>16.83</v>
       </c>
       <c r="AF6">
-        <v>-9.94</v>
+        <v>18.82</v>
       </c>
       <c r="AG6">
-        <v>181.53</v>
+        <v>11.84</v>
       </c>
       <c r="AH6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AK6">
-        <v>55.01544364170415</v>
+        <v>5.632045024599612</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1348,46 +1294,46 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>91.09730848861284</v>
+        <v>95.24793388429752</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>377</v>
       </c>
       <c r="D7">
-        <v>205.63</v>
+        <v>64.56</v>
       </c>
       <c r="E7">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="F7">
-        <v>0.5436634759014196</v>
+        <v>-0.6799779104945799</v>
       </c>
       <c r="G7">
-        <v>1.52</v>
+        <v>2.29</v>
       </c>
       <c r="H7">
-        <v>-0.3096918565999972</v>
+        <v>0.2477049624406397</v>
       </c>
       <c r="I7">
-        <v>199.2840057373047</v>
+        <v>63.9099983215332</v>
       </c>
       <c r="J7">
-        <v>190.6885009765625</v>
+        <v>62.50999965667724</v>
       </c>
       <c r="K7">
-        <v>192.9574005126953</v>
+        <v>61.47659980773926</v>
       </c>
       <c r="L7">
-        <v>172.8979000091553</v>
+        <v>50.61729995727539</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1399,58 +1345,58 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>128.5</v>
+        <v>37.25</v>
       </c>
       <c r="Y7">
-        <v>207.05</v>
+        <v>65.37</v>
       </c>
       <c r="Z7">
-        <v>81.13</v>
+        <v>8.9</v>
       </c>
       <c r="AA7">
-        <v>1083.73</v>
+        <v>0.1</v>
       </c>
       <c r="AB7">
-        <v>88.89</v>
+        <v>725</v>
       </c>
       <c r="AC7">
-        <v>87.5</v>
+        <v>8300</v>
       </c>
       <c r="AD7">
-        <v>3.89</v>
+        <v>17.99</v>
       </c>
       <c r="AE7">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AF7">
-        <v>-63.41</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>156.25</v>
+        <v>1900</v>
       </c>
       <c r="AH7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AI7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AK7">
-        <v>54.6789077210577</v>
+        <v>78.55108413387113</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1458,49 +1404,49 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>92.96066252587993</v>
+        <v>99.17355371900827</v>
       </c>
       <c r="C8">
-        <v>200</v>
+        <v>437</v>
       </c>
       <c r="D8">
-        <v>135.7</v>
+        <v>40.5</v>
       </c>
       <c r="E8">
-        <v>1.09</v>
+        <v>4.07</v>
       </c>
       <c r="F8">
-        <v>-0.4187539767300951</v>
+        <v>2.611404528601524</v>
       </c>
       <c r="G8">
-        <v>0.91</v>
+        <v>3.22</v>
       </c>
       <c r="H8">
-        <v>-1.271076246045282</v>
+        <v>1.790331849068731</v>
       </c>
       <c r="I8">
-        <v>135.6399993896484</v>
+        <v>40.16999969482422</v>
       </c>
       <c r="J8">
-        <v>132.1900005340576</v>
+        <v>37.99249992370606</v>
       </c>
       <c r="K8">
-        <v>126.5434005737305</v>
+        <v>35.84699989318847</v>
       </c>
       <c r="L8">
-        <v>108.4438998031616</v>
+        <v>29.54874996185303</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1509,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
         <v>1</v>
@@ -1518,49 +1464,49 @@
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>81.04000000000001</v>
+        <v>18.05</v>
       </c>
       <c r="Y8">
-        <v>137.6</v>
+        <v>43.15</v>
       </c>
       <c r="Z8">
-        <v>41.52</v>
-      </c>
-      <c r="AA8">
-        <v>17.52</v>
+        <v>2.26</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>52</v>
       </c>
       <c r="AB8">
-        <v>18.77</v>
+        <v>101.85</v>
       </c>
       <c r="AC8">
-        <v>88.41</v>
+        <v>6700</v>
       </c>
       <c r="AD8">
-        <v>10.75</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AE8">
-        <v>0.78</v>
+        <v>248.72</v>
       </c>
       <c r="AF8">
-        <v>34.38</v>
+        <v>157.35</v>
       </c>
       <c r="AG8">
-        <v>39.13</v>
+        <v>-3500</v>
       </c>
       <c r="AH8" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="AI8" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AK8">
-        <v>44.50556305490592</v>
+        <v>56.15509325706289</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1568,49 +1514,49 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>91.7184265010352</v>
+        <v>99.79338842975206</v>
       </c>
       <c r="C9">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D9">
-        <v>230.21</v>
+        <v>47.12</v>
       </c>
       <c r="E9">
-        <v>0.87</v>
+        <v>2.03</v>
       </c>
       <c r="F9">
-        <v>-0.8692472524299533</v>
+        <v>0.1519099587275118</v>
       </c>
       <c r="G9">
-        <v>1.32</v>
+        <v>2.91</v>
       </c>
       <c r="H9">
-        <v>-0.6248998531394346</v>
+        <v>1.276122886859367</v>
       </c>
       <c r="I9">
-        <v>227.4819976806641</v>
+        <v>46.07799911499023</v>
       </c>
       <c r="J9">
-        <v>226.6525009155274</v>
+        <v>45.13799953460693</v>
       </c>
       <c r="K9">
-        <v>221.0052008056641</v>
+        <v>44.17779983520508</v>
       </c>
       <c r="L9">
-        <v>193.661350402832</v>
+        <v>30.99652487754822</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1619,58 +1565,58 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>142.04</v>
+        <v>16.57</v>
       </c>
       <c r="Y9">
-        <v>236.39</v>
+        <v>48.65</v>
       </c>
       <c r="Z9">
-        <v>50.7</v>
+        <v>2.67</v>
       </c>
       <c r="AA9">
-        <v>2.62</v>
+        <v>12.29</v>
       </c>
       <c r="AB9">
-        <v>11.99</v>
+        <v>2216.67</v>
       </c>
       <c r="AC9">
-        <v>107.97</v>
+        <v>20.59</v>
       </c>
       <c r="AD9">
-        <v>2.88</v>
+        <v>0.79</v>
       </c>
       <c r="AE9">
-        <v>-11.15</v>
+        <v>-81.53</v>
       </c>
       <c r="AF9">
-        <v>-15.45</v>
+        <v>164.29</v>
       </c>
       <c r="AG9">
-        <v>176.81</v>
+        <v>147.06</v>
       </c>
       <c r="AH9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="AJ9" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AK9">
-        <v>41.16544091950821</v>
+        <v>55.00000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1678,46 +1624,46 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>92.54658385093167</v>
+        <v>92.56198347107438</v>
       </c>
       <c r="C10">
-        <v>247</v>
+        <v>397</v>
       </c>
       <c r="D10">
-        <v>57.81</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="E10">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="F10">
-        <v>-0.3573230754982962</v>
+        <v>-0.5955834889792954</v>
       </c>
       <c r="G10">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="H10">
-        <v>0.9511401295577526</v>
+        <v>-1.062698521899352</v>
       </c>
       <c r="I10">
-        <v>56.31399993896484</v>
+        <v>82.69199981689454</v>
       </c>
       <c r="J10">
-        <v>57.02849979400635</v>
+        <v>81.30050010681153</v>
       </c>
       <c r="K10">
-        <v>52.52259979248047</v>
+        <v>78.97460006713867</v>
       </c>
       <c r="L10">
-        <v>43.87340000152588</v>
+        <v>65.51079999923707</v>
       </c>
       <c r="M10">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1729,58 +1675,58 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U10" t="b">
         <v>1</v>
       </c>
       <c r="V10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>35.08</v>
+        <v>51.02</v>
       </c>
       <c r="Y10">
-        <v>58.99</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="Z10">
-        <v>12.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA10">
-        <v>15.17</v>
+        <v>149.66</v>
       </c>
       <c r="AB10">
-        <v>38.41</v>
+        <v>203.12</v>
       </c>
       <c r="AC10">
-        <v>22.64</v>
+        <v>800</v>
       </c>
       <c r="AD10">
-        <v>6.27</v>
+        <v>0.85</v>
       </c>
       <c r="AE10">
-        <v>32.65</v>
+        <v>-41.67</v>
       </c>
       <c r="AF10">
-        <v>-18.33</v>
+        <v>-20</v>
       </c>
       <c r="AG10">
-        <v>13.21</v>
+        <v>1600</v>
       </c>
       <c r="AH10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="AI10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="AJ10" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AK10">
-        <v>32.86301775067643</v>
+        <v>51.33725082701078</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1788,49 +1734,49 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>98.55072463768117</v>
+        <v>97.10743801652893</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>480</v>
       </c>
       <c r="D11">
-        <v>5.34</v>
+        <v>181.63</v>
       </c>
       <c r="E11">
-        <v>2.1</v>
+        <v>1.13</v>
       </c>
       <c r="F11">
-        <v>1.649419698073799</v>
+        <v>-0.9331611750404343</v>
       </c>
       <c r="G11">
-        <v>2.09</v>
+        <v>1.58</v>
       </c>
       <c r="H11">
-        <v>0.5886509335373995</v>
+        <v>-0.9299994348775804</v>
       </c>
       <c r="I11">
-        <v>5.08154993057251</v>
+        <v>180.4580017089844</v>
       </c>
       <c r="J11">
-        <v>4.894174981117248</v>
+        <v>177.8880004882812</v>
       </c>
       <c r="K11">
-        <v>5.052914962768555</v>
+        <v>174.6078002929688</v>
       </c>
       <c r="L11">
-        <v>4.060836238861084</v>
+        <v>147.8655333709717</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1839,58 +1785,58 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>3.333333333333333</v>
+        <v>3.888888888888888</v>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>2.38</v>
+        <v>93.11</v>
       </c>
       <c r="Y11">
-        <v>5.47</v>
+        <v>190</v>
       </c>
       <c r="Z11">
-        <v>129.88</v>
+        <v>3.95</v>
       </c>
       <c r="AA11">
-        <v>2903.8</v>
+        <v>125.16</v>
       </c>
       <c r="AB11">
-        <v>27.27</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="AC11">
-        <v>16.78</v>
+        <v>117.06</v>
       </c>
       <c r="AD11">
-        <v>13.19</v>
+        <v>39.61</v>
       </c>
       <c r="AE11">
-        <v>42.04</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="AF11">
-        <v>13.95</v>
+        <v>-24.52</v>
       </c>
       <c r="AG11">
-        <v>-27.85</v>
+        <v>62.79</v>
       </c>
       <c r="AH11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AI11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AK11">
-        <v>31.3312291430306</v>
+        <v>30.5666070112504</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1898,52 +1844,49 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>97.51552795031056</v>
+        <v>97.31404958677686</v>
       </c>
       <c r="C12">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="D12">
-        <v>296.67</v>
+        <v>32.08</v>
       </c>
       <c r="E12">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="F12">
-        <v>-1.012586021970817</v>
+        <v>-0.366512916294951</v>
       </c>
       <c r="G12">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="H12">
-        <v>-1.113472247775563</v>
+        <v>-0.8802372772444161</v>
       </c>
       <c r="I12">
-        <v>296.5140014648438</v>
+        <v>32.01699981689453</v>
       </c>
       <c r="J12">
-        <v>292.6934997558594</v>
+        <v>31.78083333969116</v>
       </c>
       <c r="K12">
-        <v>275.8732006835937</v>
+        <v>30.66520000457764</v>
       </c>
       <c r="L12">
-        <v>228.879200592041</v>
+        <v>25.72862497329712</v>
       </c>
       <c r="M12">
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.07</v>
-      </c>
-      <c r="O12" t="s">
-        <v>58</v>
+        <v>1.04</v>
       </c>
       <c r="P12">
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1952,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>7.222222222222221</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="U12" t="b">
         <v>1</v>
@@ -1961,49 +1904,49 @@
         <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>156.67</v>
+        <v>18.02</v>
       </c>
       <c r="Y12">
-        <v>299.33</v>
+        <v>32.87</v>
       </c>
       <c r="Z12">
-        <v>154.13</v>
+        <v>7.19</v>
       </c>
       <c r="AA12">
-        <v>4.6</v>
+        <v>841.8099999999999</v>
       </c>
       <c r="AB12">
-        <v>19.81</v>
+        <v>37.05</v>
       </c>
       <c r="AC12">
-        <v>8.210000000000001</v>
+        <v>58.22</v>
       </c>
       <c r="AD12">
-        <v>158.08</v>
+        <v>-4.04</v>
       </c>
       <c r="AE12">
-        <v>4.12</v>
+        <v>60.01</v>
       </c>
       <c r="AF12">
-        <v>13.23</v>
+        <v>-159.22</v>
       </c>
       <c r="AG12">
-        <v>-8.210000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="AH12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AI12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="AJ12" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AK12">
-        <v>26.82009186468274</v>
+        <v>27.79650916833119</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2011,43 +1954,43 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>95.65217391304348</v>
+        <v>99.58677685950413</v>
       </c>
       <c r="C13">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D13">
-        <v>183.22</v>
+        <v>70.91</v>
       </c>
       <c r="E13">
-        <v>1.23</v>
+        <v>3.1</v>
       </c>
       <c r="F13">
-        <v>-0.1320764376483675</v>
+        <v>1.441938973318293</v>
       </c>
       <c r="G13">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="H13">
-        <v>0.7620153316340906</v>
+        <v>0.9609625551826606</v>
       </c>
       <c r="I13">
-        <v>178.55</v>
+        <v>74.31800079345703</v>
       </c>
       <c r="J13">
-        <v>175.7980003356934</v>
+        <v>72.7450008392334</v>
       </c>
       <c r="K13">
-        <v>177.9274008178711</v>
+        <v>70.00820037841797</v>
       </c>
       <c r="L13">
-        <v>152.1768003845215</v>
+        <v>59.86180004119873</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2065,55 +2008,55 @@
         <v>0</v>
       </c>
       <c r="U13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>103.77</v>
+        <v>29.23</v>
       </c>
       <c r="Y13">
-        <v>186.27</v>
+        <v>81.72</v>
       </c>
       <c r="Z13">
-        <v>90.94</v>
+        <v>7.55</v>
       </c>
       <c r="AA13">
-        <v>20.94</v>
+        <v>-0.67</v>
       </c>
       <c r="AB13">
-        <v>8.539999999999999</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="AC13">
-        <v>24.69</v>
+        <v>58</v>
       </c>
       <c r="AD13">
-        <v>5.93</v>
+        <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>18.82</v>
+        <v>119.04</v>
       </c>
       <c r="AF13">
-        <v>11.84</v>
+        <v>-310.66</v>
       </c>
       <c r="AG13">
-        <v>-6.17</v>
+        <v>294</v>
       </c>
       <c r="AH13" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI13" t="s">
         <v>69</v>
       </c>
-      <c r="AI13" t="s">
-        <v>76</v>
-      </c>
       <c r="AJ13" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AK13">
-        <v>20.51845784852288</v>
+        <v>26.23559799696525</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2121,49 +2064,49 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>92.7536231884058</v>
+        <v>93.80165289256198</v>
       </c>
       <c r="C14">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="D14">
-        <v>131.66</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="E14">
-        <v>0.82</v>
+        <v>1.14</v>
       </c>
       <c r="F14">
-        <v>-0.9716320878162846</v>
+        <v>-0.9211048291096793</v>
       </c>
       <c r="G14">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="H14">
-        <v>-0.7982642512361254</v>
+        <v>-1.228572380676566</v>
       </c>
       <c r="I14">
-        <v>128.3759994506836</v>
+        <v>65.92200012207032</v>
       </c>
       <c r="J14">
-        <v>127.7670001983643</v>
+        <v>64.0345006942749</v>
       </c>
       <c r="K14">
-        <v>126.1917999267578</v>
+        <v>58.99640029907226</v>
       </c>
       <c r="L14">
-        <v>111.7858999633789</v>
+        <v>52.94780014038086</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2172,58 +2115,58 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>0.5555555555555555</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U14" t="b">
         <v>1</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14">
-        <v>79.89</v>
+        <v>40.75</v>
       </c>
       <c r="Y14">
-        <v>132.49</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="Z14">
-        <v>10.74</v>
+        <v>7.96</v>
       </c>
       <c r="AA14">
-        <v>19.48</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB14">
-        <v>2.43</v>
+        <v>20.27</v>
       </c>
       <c r="AC14">
-        <v>28.77</v>
+        <v>105.77</v>
       </c>
       <c r="AD14">
-        <v>23.63</v>
+        <v>-40.69</v>
       </c>
       <c r="AE14">
-        <v>4.44</v>
+        <v>105.77</v>
       </c>
       <c r="AF14">
-        <v>12.5</v>
+        <v>-7.14</v>
       </c>
       <c r="AG14">
-        <v>9.59</v>
+        <v>7.69</v>
       </c>
       <c r="AH14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AI14" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="AJ14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AK14">
-        <v>13.32111609130075</v>
+        <v>16.29116421379137</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2231,43 +2174,43 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>98.9648033126294</v>
+        <v>98.7603305785124</v>
       </c>
       <c r="C15">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="D15">
-        <v>3520.51</v>
+        <v>86</v>
       </c>
       <c r="E15">
-        <v>0.96</v>
+        <v>1.43</v>
       </c>
       <c r="F15">
-        <v>-0.6849545487345569</v>
+        <v>-0.5714707971177855</v>
       </c>
       <c r="G15">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>-0.4515354550427442</v>
+        <v>-0.2333292280132813</v>
       </c>
       <c r="I15">
-        <v>3529.380029296875</v>
+        <v>85.90999908447266</v>
       </c>
       <c r="J15">
-        <v>3444.269995117188</v>
+        <v>85.99599990844726</v>
       </c>
       <c r="K15">
-        <v>3366.702788085937</v>
+        <v>83.11620010375977</v>
       </c>
       <c r="L15">
-        <v>2715.17424621582</v>
+        <v>68.55025011062622</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2288,52 +2231,52 @@
         <v>1</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
         <v>0</v>
       </c>
       <c r="X15">
-        <v>1661.54</v>
+        <v>38.43</v>
       </c>
       <c r="Y15">
-        <v>3599.7</v>
+        <v>89.63</v>
       </c>
       <c r="Z15">
-        <v>12.17</v>
+        <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>5.62</v>
       </c>
       <c r="AB15">
-        <v>4.08</v>
+        <v>29.23</v>
       </c>
       <c r="AC15">
-        <v>8.75</v>
+        <v>29.41</v>
       </c>
       <c r="AD15">
-        <v>9.82</v>
+        <v>-4.31</v>
       </c>
       <c r="AE15">
-        <v>9.630000000000001</v>
+        <v>-200</v>
       </c>
       <c r="AF15">
-        <v>42.04</v>
+        <v>69.23</v>
       </c>
       <c r="AG15">
-        <v>-30.17</v>
+        <v>23.53</v>
       </c>
       <c r="AH15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AI15" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="AJ15" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AK15">
-        <v>4.273797565305879</v>
+        <v>11.43600914503382</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2341,43 +2284,43 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>95.03105590062113</v>
+        <v>98.34710743801654</v>
       </c>
       <c r="C16">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="D16">
-        <v>44.58</v>
+        <v>114.21</v>
       </c>
       <c r="E16">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="F16">
-        <v>0.3388938051287568</v>
+        <v>-0.2097804191951367</v>
       </c>
       <c r="G16">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="H16">
-        <v>-0.08904625902239109</v>
+        <v>0.2808797341960826</v>
       </c>
       <c r="I16">
-        <v>43.51600036621094</v>
+        <v>112.4860000610352</v>
       </c>
       <c r="J16">
-        <v>42.07549991607666</v>
+        <v>111.7810001373291</v>
       </c>
       <c r="K16">
-        <v>42.30699996948242</v>
+        <v>107.821600189209</v>
       </c>
       <c r="L16">
-        <v>36.38380001068115</v>
+        <v>86.03240009307861</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P16">
         <v>2</v>
@@ -2401,599 +2344,49 @@
         <v>1</v>
       </c>
       <c r="W16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>25.45</v>
+        <v>59.88</v>
       </c>
       <c r="Y16">
-        <v>44.73</v>
+        <v>118.45</v>
       </c>
       <c r="Z16">
-        <v>7.49</v>
+        <v>4.72</v>
       </c>
       <c r="AA16">
-        <v>12.49</v>
+        <v>11833.33</v>
       </c>
       <c r="AB16">
-        <v>1180</v>
+        <v>18.99</v>
       </c>
       <c r="AC16">
-        <v>57.58</v>
+        <v>46.55</v>
       </c>
       <c r="AD16">
-        <v>4.9</v>
+        <v>17.37</v>
       </c>
       <c r="AE16">
-        <v>-40.91</v>
+        <v>136.11</v>
       </c>
       <c r="AF16">
-        <v>104.65</v>
+        <v>5.88</v>
       </c>
       <c r="AG16">
-        <v>30.3</v>
+        <v>-41.38</v>
       </c>
       <c r="AH16" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="AI16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="AJ16" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AK16">
-        <v>75.83164178390287</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17">
-        <v>97.10144927536231</v>
-      </c>
-      <c r="C17">
-        <v>276</v>
-      </c>
-      <c r="D17">
-        <v>32.13</v>
-      </c>
-      <c r="E17">
-        <v>1.79</v>
-      </c>
-      <c r="F17">
-        <v>1.014633718678544</v>
-      </c>
-      <c r="G17">
-        <v>2.31</v>
-      </c>
-      <c r="H17">
-        <v>0.9353797297307811</v>
-      </c>
-      <c r="I17">
-        <v>31.83400001525879</v>
-      </c>
-      <c r="J17">
-        <v>30.56800012588501</v>
-      </c>
-      <c r="K17">
-        <v>29.14959991455078</v>
-      </c>
-      <c r="L17">
-        <v>22.09172493934631</v>
-      </c>
-      <c r="M17">
-        <v>1.04</v>
-      </c>
-      <c r="N17">
-        <v>1.09</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" t="b">
-        <v>1</v>
-      </c>
-      <c r="V17" t="b">
-        <v>1</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>15.42</v>
-      </c>
-      <c r="Y17">
-        <v>33.08</v>
-      </c>
-      <c r="Z17">
-        <v>2.02</v>
-      </c>
-      <c r="AA17">
-        <v>16.02</v>
-      </c>
-      <c r="AB17">
-        <v>615.38</v>
-      </c>
-      <c r="AC17">
-        <v>72.09</v>
-      </c>
-      <c r="AD17">
-        <v>7.76</v>
-      </c>
-      <c r="AE17">
-        <v>164.29</v>
-      </c>
-      <c r="AF17">
-        <v>147.06</v>
-      </c>
-      <c r="AG17">
-        <v>-73.64</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK17">
-        <v>70.5941893230497</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37">
-      <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18">
-        <v>99.79296066252587</v>
-      </c>
-      <c r="C18">
-        <v>36</v>
-      </c>
-      <c r="D18">
-        <v>14.54</v>
-      </c>
-      <c r="E18">
-        <v>1.62</v>
-      </c>
-      <c r="F18">
-        <v>0.6665252783650174</v>
-      </c>
-      <c r="G18">
-        <v>2.64</v>
-      </c>
-      <c r="H18">
-        <v>1.455472924020853</v>
-      </c>
-      <c r="I18">
-        <v>14.69425010681152</v>
-      </c>
-      <c r="J18">
-        <v>14.40337505340576</v>
-      </c>
-      <c r="K18">
-        <v>13.90755001068115</v>
-      </c>
-      <c r="L18">
-        <v>10.90942499637604</v>
-      </c>
-      <c r="M18">
-        <v>1.02</v>
-      </c>
-      <c r="N18">
-        <v>1.06</v>
-      </c>
-      <c r="P18">
-        <v>4</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>2.222222222222222</v>
-      </c>
-      <c r="U18" t="b">
-        <v>1</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>5.46</v>
-      </c>
-      <c r="Y18">
-        <v>15.35</v>
-      </c>
-      <c r="Z18">
-        <v>3.76</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB18">
-        <v>58.13</v>
-      </c>
-      <c r="AC18">
-        <v>121.69</v>
-      </c>
-      <c r="AD18">
-        <v>8.77</v>
-      </c>
-      <c r="AE18">
-        <v>29.58</v>
-      </c>
-      <c r="AF18">
-        <v>22.41</v>
-      </c>
-      <c r="AG18">
-        <v>39.76</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK18">
-        <v>57.34297561823342</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19">
-        <v>99.37888198757764</v>
-      </c>
-      <c r="C19">
-        <v>78</v>
-      </c>
-      <c r="D19">
-        <v>28.55</v>
-      </c>
-      <c r="E19">
-        <v>1.63</v>
-      </c>
-      <c r="F19">
-        <v>0.6870022454422833</v>
-      </c>
-      <c r="G19">
-        <v>1.72</v>
-      </c>
-      <c r="H19">
-        <v>0.005516139939440249</v>
-      </c>
-      <c r="I19">
-        <v>28.56399955749512</v>
-      </c>
-      <c r="J19">
-        <v>28.04199991226196</v>
-      </c>
-      <c r="K19">
-        <v>27.78960006713867</v>
-      </c>
-      <c r="L19">
-        <v>22.46610001564026</v>
-      </c>
-      <c r="M19">
-        <v>1.02</v>
-      </c>
-      <c r="N19">
-        <v>1.03</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>12.92</v>
-      </c>
-      <c r="Y19">
-        <v>29.78</v>
-      </c>
-      <c r="Z19">
-        <v>8.24</v>
-      </c>
-      <c r="AA19">
-        <v>-171.36</v>
-      </c>
-      <c r="AB19">
-        <v>76.29000000000001</v>
-      </c>
-      <c r="AC19">
-        <v>117.31</v>
-      </c>
-      <c r="AD19">
-        <v>5.01</v>
-      </c>
-      <c r="AE19">
-        <v>127.27</v>
-      </c>
-      <c r="AF19">
-        <v>-280.77</v>
-      </c>
-      <c r="AG19">
-        <v>83.33</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK19">
-        <v>56.37583767978125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20">
-        <v>96.68737060041408</v>
-      </c>
-      <c r="C20">
-        <v>455</v>
-      </c>
-      <c r="D20">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="E20">
-        <v>1.14</v>
-      </c>
-      <c r="F20">
-        <v>-0.3163691413437641</v>
-      </c>
-      <c r="G20">
-        <v>2.89</v>
-      </c>
-      <c r="H20">
-        <v>1.84948291969515</v>
-      </c>
-      <c r="I20">
-        <v>69.03000030517578</v>
-      </c>
-      <c r="J20">
-        <v>69.15349998474122</v>
-      </c>
-      <c r="K20">
-        <v>67.71159988403321</v>
-      </c>
-      <c r="L20">
-        <v>54.28420000076294</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1.02</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20" t="b">
-        <v>1</v>
-      </c>
-      <c r="V20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>36.8</v>
-      </c>
-      <c r="Y20">
-        <v>72.98999999999999</v>
-      </c>
-      <c r="Z20">
-        <v>3.2</v>
-      </c>
-      <c r="AA20">
-        <v>4.95</v>
-      </c>
-      <c r="AB20">
-        <v>50.47</v>
-      </c>
-      <c r="AC20">
-        <v>69.47</v>
-      </c>
-      <c r="AD20">
-        <v>-3</v>
-      </c>
-      <c r="AE20">
-        <v>69.23</v>
-      </c>
-      <c r="AF20">
-        <v>23.53</v>
-      </c>
-      <c r="AG20">
-        <v>-29.77</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK20">
-        <v>47.03949832439267</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21">
-        <v>92.13250517598344</v>
-      </c>
-      <c r="C21">
-        <v>439</v>
-      </c>
-      <c r="D21">
-        <v>116.78</v>
-      </c>
-      <c r="E21">
-        <v>0.9</v>
-      </c>
-      <c r="F21">
-        <v>-0.8078163511981543</v>
-      </c>
-      <c r="G21">
-        <v>1.15</v>
-      </c>
-      <c r="H21">
-        <v>-0.8928266501979568</v>
-      </c>
-      <c r="I21">
-        <v>115.7800003051758</v>
-      </c>
-      <c r="J21">
-        <v>114.9270004272461</v>
-      </c>
-      <c r="K21">
-        <v>111.0475999450684</v>
-      </c>
-      <c r="L21">
-        <v>94.99345008850098</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>1.04</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21" t="b">
-        <v>1</v>
-      </c>
-      <c r="V21" t="b">
-        <v>1</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-      <c r="X21">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="Y21">
-        <v>117.92</v>
-      </c>
-      <c r="Z21">
-        <v>8.84</v>
-      </c>
-      <c r="AA21">
-        <v>17.13</v>
-      </c>
-      <c r="AB21">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="AC21">
-        <v>75.70999999999999</v>
-      </c>
-      <c r="AD21">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="AE21">
-        <v>-10.22</v>
-      </c>
-      <c r="AF21">
-        <v>7.87</v>
-      </c>
-      <c r="AG21">
-        <v>81.43000000000001</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK21">
-        <v>31.7198828639492</v>
+        <v>10.47589946156172</v>
       </c>
     </row>
   </sheetData>
